--- a/content_forms/027_showcase_your_success--content_forms.xlsx
+++ b/content_forms/027_showcase_your_success--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'public',_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'public', 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'private',_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'private', 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_shared',_'label':_'not_shared'}</t>
+          <t>not_shared</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_shared', 'label': 'Not Shared'}</t>
+          <t>Not Shared</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'public',_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'public', 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'private',_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'private', 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_shared',_'label':_'not_shared'}</t>
+          <t>not_shared</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_shared', 'label': 'Not Shared'}</t>
+          <t>Not Shared</t>
         </is>
       </c>
     </row>
